--- a/doc/20251012 NXT 반영 리스트.xlsx
+++ b/doc/20251012 NXT 반영 리스트.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6600" uniqueCount="3399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6606" uniqueCount="3404">
   <si>
     <t>2025-09-03 09:48:22/tab/AXISFILE.INI</t>
   </si>
@@ -10452,6 +10452,26 @@
   </si>
   <si>
     <t>호가설정판좌측하단.BMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파일 옮기기 이미 운영 반영 되있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면 권한 관련</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NXT 관련 문구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000 화면 관련</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20030,6 +20050,9 @@
       <c r="E8" t="s">
         <v>1890</v>
       </c>
+      <c r="F8" t="s">
+        <v>3399</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
@@ -20044,6 +20067,9 @@
       <c r="E9" t="s">
         <v>1890</v>
       </c>
+      <c r="F9" t="s">
+        <v>3400</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
@@ -20058,6 +20084,9 @@
       <c r="E10" t="s">
         <v>1890</v>
       </c>
+      <c r="F10" t="s">
+        <v>3401</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
@@ -20072,6 +20101,9 @@
       <c r="E11" t="s">
         <v>1890</v>
       </c>
+      <c r="F11" t="s">
+        <v>3402</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
@@ -20100,6 +20132,9 @@
       <c r="E13" t="s">
         <v>1890</v>
       </c>
+      <c r="F13" t="s">
+        <v>3403</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
@@ -20113,6 +20148,9 @@
       </c>
       <c r="E14" t="s">
         <v>1890</v>
+      </c>
+      <c r="F14" t="s">
+        <v>3403</v>
       </c>
     </row>
     <row r="15" spans="1:6">
